--- a/Lab_4/data/partB/param_optimization_process/v100_k20_s100_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v100_k20_s100_results.xlsx
@@ -518,37 +518,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>29</v>
       </c>
       <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L2" t="n">
         <v>4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>7</v>
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -591,10 +591,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,16 +646,16 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -674,22 +674,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -698,25 +698,25 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>2</v>
       </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3</v>
-      </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -741,13 +741,13 @@
         <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
@@ -756,16 +756,16 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
         <v>9</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>6</v>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -787,19 +787,19 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -814,13 +814,13 @@
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
         <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -845,13 +845,13 @@
         <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -860,19 +860,19 @@
         <v>10</v>
       </c>
       <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="n">
         <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>6</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -885,7 +885,7 @@
         <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -894,37 +894,37 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
         <v>4</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -937,13 +937,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -958,13 +958,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -995,13 +995,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
@@ -1010,10 +1010,10 @@
         <v>30</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1022,13 +1022,13 @@
         <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
         <v>2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1041,16 +1041,16 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1059,16 +1059,16 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1093,28 +1093,28 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1126,7 +1126,7 @@
         <v>59</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O13" t="n">
         <v>5</v>
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1157,22 +1157,22 @@
         <v>21</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>5</v>
@@ -1184,7 +1184,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -1200,13 +1200,13 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1215,16 +1215,16 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
         <v>4</v>
@@ -1233,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1249,46 +1249,46 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="n">
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>4</v>
       </c>
-      <c r="F16" t="n">
-        <v>6</v>
-      </c>
-      <c r="G16" t="n">
-        <v>5</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
+      <c r="M16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
+      <c r="N16" t="n">
         <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>4</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11331,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11705,7 +11705,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11875,7 +11875,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13660,7 +13660,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13813,7 +13813,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13881,7 +13881,7 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -14323,7 +14323,7 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14578,7 +14578,7 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -14663,7 +14663,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14799,7 +14799,7 @@
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15496,7 +15496,7 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15853,7 +15853,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16448,7 +16448,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17757,7 +17757,7 @@
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17995,7 +17995,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18148,7 +18148,7 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18165,7 +18165,7 @@
       </c>
       <c r="C992" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="C993" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18607,7 +18607,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18658,7 +18658,7 @@
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -19270,7 +19270,7 @@
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19389,7 +19389,7 @@
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="C1084" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20222,7 +20222,7 @@
       </c>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20732,7 +20732,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20851,7 +20851,7 @@
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20936,7 +20936,7 @@
       </c>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21412,7 +21412,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21565,7 +21565,7 @@
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21718,7 +21718,7 @@
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -21752,7 +21752,7 @@
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21769,7 +21769,7 @@
       </c>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21871,7 +21871,7 @@
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21888,7 +21888,7 @@
       </c>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21956,7 +21956,7 @@
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22007,7 +22007,7 @@
       </c>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="C1220" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="C1233" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22279,7 +22279,7 @@
       </c>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22296,7 +22296,7 @@
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22330,7 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22432,7 @@
       </c>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22500,7 +22500,7 @@
       </c>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22517,7 +22517,7 @@
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22551,7 +22551,7 @@
       </c>
       <c r="C1250" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22755,7 +22755,7 @@
       </c>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22789,7 +22789,7 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22993,7 +22993,7 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23299,7 +23299,7 @@
       </c>
       <c r="C1294" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -23775,7 +23775,7 @@
       </c>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23792,7 +23792,7 @@
       </c>
       <c r="C1323" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23877,7 +23877,7 @@
       </c>
       <c r="C1328" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23928,7 +23928,7 @@
       </c>
       <c r="C1331" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24013,7 +24013,7 @@
       </c>
       <c r="C1336" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24064,7 +24064,7 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24098,7 +24098,7 @@
       </c>
       <c r="C1341" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24183,7 +24183,7 @@
       </c>
       <c r="C1346" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="C1347" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24370,7 +24370,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24489,7 +24489,7 @@
       </c>
       <c r="C1364" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24506,7 +24506,7 @@
       </c>
       <c r="C1365" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24676,7 +24676,7 @@
       </c>
       <c r="C1375" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24693,7 +24693,7 @@
       </c>
       <c r="C1376" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25084,7 +25084,7 @@
       </c>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25118,7 +25118,7 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25135,7 +25135,7 @@
       </c>
       <c r="C1402" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25152,7 +25152,7 @@
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25186,7 +25186,7 @@
       </c>
       <c r="C1405" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25237,7 +25237,7 @@
       </c>
       <c r="C1408" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -25322,7 +25322,7 @@
       </c>
       <c r="C1413" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="C1414" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25492,7 +25492,7 @@
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25543,7 +25543,7 @@
       </c>
       <c r="C1426" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25560,7 +25560,7 @@
       </c>
       <c r="C1427" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25747,7 +25747,7 @@
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26019,7 +26019,7 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="C1456" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26223,7 +26223,7 @@
       </c>
       <c r="C1466" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26529,7 +26529,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26563,7 +26563,7 @@
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26614,7 +26614,7 @@
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26648,7 +26648,7 @@
       </c>
       <c r="C1491" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26750,7 +26750,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
